--- a/output/pdf_financials_xlsx/CRCC.xlsx
+++ b/output/pdf_financials_xlsx/CRCC.xlsx
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.007102</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.002754</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.078846</v>
+        <v>-0.085948</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.048357</v>
+        <v>-0.051111</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.014726</v>
@@ -3939,7 +3939,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>-0.007102</v>
       </c>

--- a/output/pdf_financials_xlsx/CRCC.xlsx
+++ b/output/pdf_financials_xlsx/CRCC.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.835925</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.508416</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.272727</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.835925</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.508416</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.272727</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.2149</v>
+        <v>0.378975</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.432532</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.282834</v>
+        <v>0.010107</v>
       </c>
     </row>
     <row r="49">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRCC.xlsx
+++ b/output/pdf_financials_xlsx/CRCC.xlsx
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.022108</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.023561</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.038456</v>
       </c>
     </row>
     <row r="102">
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.085948</v>
+        <v>-0.108056</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.051111</v>
+        <v>-0.074672</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.014726</v>
+        <v>0.053182</v>
       </c>
     </row>
     <row r="107">
@@ -3436,7 +3436,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>-0.022108</v>
       </c>
